--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T11:48:47+00:00</t>
+    <t>2026-06-24T12:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:48:53+00:00</t>
+    <t>2026-06-24T13:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:04:12+00:00</t>
+    <t>2026-06-24T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:28:39+00:00</t>
+    <t>2026-06-25T06:56:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T06:56:45+00:00</t>
+    <t>2026-06-25T09:36:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:36:02+00:00</t>
+    <t>2026-06-25T15:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:23:55+00:00</t>
+    <t>2026-06-26T06:54:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T06:54:57+00:00</t>
+    <t>2026-06-26T07:46:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
